--- a/astro-site/public/dl/guia-dark-kitchen/checklist-apertura-legal.xlsx
+++ b/astro-site/public/dl/guia-dark-kitchen/checklist-apertura-legal.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Apertura Legal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Checklist Apertura Legal'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -510,7 +512,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -539,6 +541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1639,7 +1642,7 @@
       </c>
       <c r="F40" s="13">
         <f>SUM(F5:F39)</f>
-        <v/>
+        <v>7330.0</v>
       </c>
     </row>
   </sheetData>
@@ -1652,6 +1655,15 @@
       <formula1>"Pendiente,En Proceso,Completado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>